--- a/public/downloads/Baserarole2024.xlsx
+++ b/public/downloads/Baserarole2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>54</v>
       </c>
       <c r="N3" s="5">
-        <v>711.4557731151581</v>
+        <v>711455.7731151581</v>
       </c>
       <c r="O3" s="4">
-        <v>0.04149397953546938</v>
+        <v>41.49397953546939</v>
       </c>
       <c r="P3" s="5">
         <v>17146</v>
@@ -709,10 +732,10 @@
         <v>54</v>
       </c>
       <c r="N4" s="5">
-        <v>1562.952919960022</v>
+        <v>1562952.919960022</v>
       </c>
       <c r="O4" s="4">
-        <v>0.1342512386153601</v>
+        <v>134.2512386153601</v>
       </c>
       <c r="P4" s="5">
         <v>11642</v>
@@ -759,10 +782,10 @@
         <v>54</v>
       </c>
       <c r="N5" s="5">
-        <v>2036.761655330658</v>
+        <v>2036761.655330658</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1894662004958751</v>
+        <v>189.4662004958751</v>
       </c>
       <c r="P5" s="5">
         <v>10750</v>
@@ -809,10 +832,10 @@
         <v>54</v>
       </c>
       <c r="N6" s="5">
-        <v>1474.97678232193</v>
+        <v>1474976.78232193</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1506000390363416</v>
+        <v>150.6000390363417</v>
       </c>
       <c r="P6" s="5">
         <v>9794</v>
@@ -859,10 +882,10 @@
         <v>54</v>
       </c>
       <c r="N7" s="5">
-        <v>4857.508912801743</v>
+        <v>4857508.912801743</v>
       </c>
       <c r="O7" s="4">
-        <v>0.6637754731896341</v>
+        <v>663.7754731896341</v>
       </c>
       <c r="P7" s="5">
         <v>7318</v>
@@ -909,10 +932,10 @@
         <v>54</v>
       </c>
       <c r="N8" s="5">
-        <v>403.1707570552826</v>
+        <v>403170.7570552826</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03828782118283786</v>
+        <v>38.28782118283785</v>
       </c>
       <c r="P8" s="5">
         <v>10530</v>
@@ -959,10 +982,10 @@
         <v>54</v>
       </c>
       <c r="N9" s="5">
-        <v>550.5065805912018</v>
+        <v>550506.5805912018</v>
       </c>
       <c r="O9" s="4">
-        <v>0.05628901642036828</v>
+        <v>56.28901642036828</v>
       </c>
       <c r="P9" s="5">
         <v>9780</v>
@@ -1009,10 +1032,10 @@
         <v>54</v>
       </c>
       <c r="N10" s="5">
-        <v>728.7659356594086</v>
+        <v>728765.9356594086</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08745541049554885</v>
+        <v>87.45541049554885</v>
       </c>
       <c r="P10" s="5">
         <v>8333</v>
@@ -1059,10 +1082,10 @@
         <v>54</v>
       </c>
       <c r="N11" s="5">
-        <v>818.6691610813141</v>
+        <v>818669.1610813141</v>
       </c>
       <c r="O11" s="4">
-        <v>0.07398727167476855</v>
+        <v>73.98727167476855</v>
       </c>
       <c r="P11" s="5">
         <v>11065</v>
@@ -1109,10 +1132,10 @@
         <v>54</v>
       </c>
       <c r="N12" s="5">
-        <v>395.1976673603058</v>
+        <v>395197.6673603058</v>
       </c>
       <c r="O12" s="4">
-        <v>0.04062058457809701</v>
+        <v>40.62058457809701</v>
       </c>
       <c r="P12" s="5">
         <v>9729</v>
@@ -1159,10 +1182,10 @@
         <v>54</v>
       </c>
       <c r="N13" s="5">
-        <v>1205.536176919937</v>
+        <v>1205536.176919937</v>
       </c>
       <c r="O13" s="4">
-        <v>0.0889891619487663</v>
+        <v>88.9891619487663</v>
       </c>
       <c r="P13" s="5">
         <v>13547</v>
@@ -1209,10 +1232,10 @@
         <v>54</v>
       </c>
       <c r="N14" s="5">
-        <v>25643.82821989059</v>
+        <v>25643828.21989059</v>
       </c>
       <c r="O14" s="4">
-        <v>1.039769217852272</v>
+        <v>1039.769217852272</v>
       </c>
       <c r="P14" s="5">
         <v>24663</v>
@@ -1259,10 +1282,10 @@
         <v>54</v>
       </c>
       <c r="N15" s="5">
-        <v>7782.353778600693</v>
+        <v>7782353.778600693</v>
       </c>
       <c r="O15" s="4">
-        <v>0.9258093955032944</v>
+        <v>925.8093955032945</v>
       </c>
       <c r="P15" s="5">
         <v>8406</v>
@@ -1309,10 +1332,10 @@
         <v>54</v>
       </c>
       <c r="N16" s="5">
-        <v>6295.81214594841</v>
+        <v>6295812.14594841</v>
       </c>
       <c r="O16" s="4">
-        <v>0.167215004805939</v>
+        <v>167.215004805939</v>
       </c>
       <c r="P16" s="5">
         <v>37651</v>
@@ -1359,10 +1382,10 @@
         <v>54</v>
       </c>
       <c r="N17" s="5">
-        <v>1857.541911125183</v>
+        <v>1857541.911125183</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1796983564985183</v>
+        <v>179.6983564985183</v>
       </c>
       <c r="P17" s="5">
         <v>10337</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2498905806953123</v>
+        <v>0.3144408323398261</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2471773247812184</v>
+        <v>0.2615481180108551</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2613961146695655</v>
+        <v>0.2934816848664016</v>
       </c>
       <c r="E3" s="4">
-        <v>93.65306122448979</v>
+        <v>89.41326530612245</v>
       </c>
       <c r="F3" s="4">
-        <v>91.67953020134229</v>
+        <v>81.61241610738254</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1746248426451662</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2998088782463817</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2402235196532846</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2081441263124764</v>
+        <v>0.2449440356434071</v>
       </c>
       <c r="C4" s="4">
-        <v>0.201969247502731</v>
+        <v>0.230994259459507</v>
       </c>
       <c r="D4" s="4">
-        <v>0.169375367512869</v>
+        <v>0.2144153492534156</v>
       </c>
       <c r="E4" s="4">
-        <v>92.54591836734694</v>
+        <v>90.5204081632653</v>
       </c>
       <c r="F4" s="4">
-        <v>89.69351230425055</v>
+        <v>82.25503355704699</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.03155434850083812</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2417886007933233</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2246833897593394</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2516819919577795</v>
+        <v>0.3204985249105499</v>
       </c>
       <c r="C5" s="4">
-        <v>0.18833311991302</v>
+        <v>0.2152585811838937</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1737881801579077</v>
+        <v>0.2456287359136822</v>
       </c>
       <c r="E5" s="4">
-        <v>87.54130223518044</v>
+        <v>84.91982507288635</v>
       </c>
       <c r="F5" s="4">
-        <v>81.16011505273292</v>
+        <v>75.26126558005875</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1227158976524091</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3371515617941143</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2002580060075241</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,116 +1797,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3787189778244652</v>
+        <v>0.4674147311402407</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3564327176348865</v>
+        <v>0.4187054574128745</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3845018681442894</v>
+        <v>0.3877101962092297</v>
       </c>
       <c r="E3" s="4">
-        <v>86.21598639455782</v>
+        <v>88.79421768707483</v>
       </c>
       <c r="F3" s="4">
-        <v>81.45637583892621</v>
+        <v>84.31487695749439</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3561315991860751</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3744568127597489</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2550404511267192</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2293900624296583</v>
+        <v>0.4326521421641673</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2630766572607222</v>
+        <v>0.4455660431316376</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2513300718370374</v>
+        <v>0.4199537779063547</v>
       </c>
       <c r="E4" s="4">
-        <v>86.24149659863946</v>
+        <v>89.96258503401361</v>
       </c>
       <c r="F4" s="4">
-        <v>80.19071588366886</v>
+        <v>85.5592841163311</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3488323414972629</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3084969334062066</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2965167527812968</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3096839765481799</v>
+        <v>0.6172616482573565</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2799123605400887</v>
+        <v>0.6432100971270607</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2891145025092377</v>
+        <v>0.6276417119954983</v>
       </c>
       <c r="E5" s="4">
-        <v>82.30563654033081</v>
+        <v>86.81972789115653</v>
       </c>
       <c r="F5" s="4">
-        <v>74.28092042185854</v>
+        <v>79.30249280920302</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -1796,9 +1974,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.6432100971270607</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3749129016517666</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.223375177137774</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,107 +2097,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4615891654953629</v>
+        <v>0.2498905806953123</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4838581406704794</v>
+        <v>0.2471773247812184</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5309491896435503</v>
+        <v>0.2613961146695655</v>
       </c>
       <c r="E3" s="4">
-        <v>90.60374149659864</v>
+        <v>93.65306122448979</v>
       </c>
       <c r="F3" s="4">
-        <v>85.68400447427292</v>
+        <v>91.67953020134229</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2306733230146552</v>
+      </c>
+      <c r="O3" s="5">
+        <v>19</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1368690918498356</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1403480377341195</v>
+      </c>
+      <c r="R3" s="5">
+        <v>19</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3051463041259581</v>
+        <v>0.2081441263124764</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2983720775867315</v>
+        <v>0.201969247502731</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2785850586740707</v>
+        <v>0.169375367512869</v>
       </c>
       <c r="E4" s="4">
-        <v>90.24489795918367</v>
+        <v>92.54591836734694</v>
       </c>
       <c r="F4" s="4">
-        <v>83.48266219239372</v>
+        <v>89.69351230425055</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1728167069219769</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1204728463818312</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1187793058347875</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4824592978888843</v>
+        <v>0.2516819919577795</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3941396777290151</v>
+        <v>0.18833311991302</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3994308725076751</v>
+        <v>0.1737881801579077</v>
       </c>
       <c r="E5" s="4">
-        <v>86.1370262390675</v>
+        <v>87.54130223518044</v>
       </c>
       <c r="F5" s="4">
-        <v>78.6457334611686</v>
+        <v>81.16011505273292</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
@@ -1995,23 +2260,41 @@
         <v>10</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.18833311991302</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1461921277565588</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07831393401391509</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2397,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3178166657251012</v>
+        <v>0.3787189778244652</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3804064494628762</v>
+        <v>0.3564327176348865</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3754144486344018</v>
+        <v>0.3845018681442894</v>
       </c>
       <c r="E3" s="4">
-        <v>78.01020408163265</v>
+        <v>86.21598639455782</v>
       </c>
       <c r="F3" s="4">
-        <v>76.00950782997761</v>
+        <v>81.45637583892621</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3114666796215726</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2559427882265481</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2116163228613122</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.324773416911097</v>
+        <v>0.2293900624296583</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3866119127680235</v>
+        <v>0.2630766572607222</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3037990439375676</v>
+        <v>0.2513300718370374</v>
       </c>
       <c r="E4" s="4">
-        <v>78.70918367346938</v>
+        <v>86.24149659863946</v>
       </c>
       <c r="F4" s="4">
-        <v>77.41834451901566</v>
+        <v>80.19071588366886</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1226933186962746</v>
+      </c>
+      <c r="O4" s="5">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2216865622001755</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2398429100390409</v>
+      </c>
+      <c r="R4" s="5">
+        <v>16</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3582286173214259</v>
+        <v>0.3096839765481799</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4725859586035218</v>
+        <v>0.2799123605400887</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3525985913146883</v>
+        <v>0.2891145025092377</v>
       </c>
       <c r="E5" s="4">
-        <v>78.17055393586003</v>
+        <v>82.30563654033081</v>
       </c>
       <c r="F5" s="4">
-        <v>73.54985618408446</v>
+        <v>74.28092042185854</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.0009586056947088966</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3098209202188525</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2800188722839453</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3753296104471188</v>
+        <v>0.4615891654953629</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2562464351800027</v>
+        <v>0.4838581406704794</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2839742355931756</v>
+        <v>0.5309491896435503</v>
       </c>
       <c r="E3" s="4">
-        <v>27.22789115646259</v>
+        <v>90.60374149659864</v>
       </c>
       <c r="F3" s="4">
-        <v>32.32774049217002</v>
+        <v>85.68400447427292</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>4</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4797088952417017</v>
+      </c>
+      <c r="O3" s="5">
         <v>16</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="P3" s="4">
+        <v>0.2347780930253748</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2003443000829943</v>
+      </c>
+      <c r="R3" s="5">
         <v>16</v>
       </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.356372274183771</v>
+        <v>0.3051463041259581</v>
       </c>
       <c r="C4" s="4">
-        <v>0.24587614086132</v>
+        <v>0.2983720775867315</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2293738502362219</v>
+        <v>0.2785850586740707</v>
       </c>
       <c r="E4" s="4">
-        <v>28.42857142857143</v>
+        <v>90.24489795918367</v>
       </c>
       <c r="F4" s="4">
-        <v>35.12248322147651</v>
+        <v>83.48266219239372</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2311474120835174</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1788300385312226</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1622481054352048</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4265709362274067</v>
+        <v>0.4824592978888843</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2468486772273062</v>
+        <v>0.3941396777290151</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2172344818673708</v>
+        <v>0.3994308725076751</v>
       </c>
       <c r="E5" s="4">
-        <v>33.15111758989314</v>
+        <v>86.1370262390675</v>
       </c>
       <c r="F5" s="4">
-        <v>37.21716203259815</v>
+        <v>78.6457334611686</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
       </c>
       <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>4</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3390617226577263</v>
+      </c>
+      <c r="O5" s="5">
         <v>10</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="P5" s="4">
+        <v>0.2567793438984268</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1907026441343794</v>
+      </c>
+      <c r="R5" s="5">
         <v>10</v>
       </c>
-      <c r="M5" s="5">
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2997,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5708876305624691</v>
+        <v>0.3178166657251012</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6252828977480893</v>
+        <v>0.3804064494628762</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6416735553548568</v>
+        <v>0.3754144486344018</v>
       </c>
       <c r="E3" s="4">
-        <v>92.078231292517</v>
+        <v>78.01020408163265</v>
       </c>
       <c r="F3" s="4">
-        <v>87.3434004474273</v>
+        <v>76.00950782997761</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3164499841596495</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3030659822812097</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2395204641468217</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4671414922135774</v>
+        <v>0.324773416911097</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5076191686266802</v>
+        <v>0.3866119127680235</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4697739470315853</v>
+        <v>0.3037990439375676</v>
       </c>
       <c r="E4" s="4">
-        <v>91.69387755102041</v>
+        <v>78.70918367346938</v>
       </c>
       <c r="F4" s="4">
-        <v>85.63982102908277</v>
+        <v>77.41834451901566</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3115584207436143</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2602623890109032</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2772274655976218</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8612211663198137</v>
+        <v>0.3582286173214259</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6779407707255439</v>
+        <v>0.4725859586035218</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7226700843902343</v>
+        <v>0.3525985913146883</v>
       </c>
       <c r="E5" s="4">
-        <v>87.00680272108823</v>
+        <v>78.17055393586003</v>
       </c>
       <c r="F5" s="4">
-        <v>80.50814956855348</v>
+        <v>73.54985618408446</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4376405310660895</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2763123117066416</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2758102904730669</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,200 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6401106538332415</v>
+        <v>0.3753296104471188</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2744333715517371</v>
+        <v>0.2562464351800027</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2634276734820404</v>
+        <v>0.2839742355931756</v>
       </c>
       <c r="E3" s="4">
-        <v>18.81122448979592</v>
+        <v>27.22789115646259</v>
       </c>
       <c r="F3" s="4">
-        <v>20.70693512304251</v>
+        <v>32.32774049217002</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3753296104471188</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2562464351800027</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8103680462182016</v>
+        <v>0.356372274183771</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2706910995568245</v>
+        <v>0.24587614086132</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4172317315680235</v>
+        <v>0.2293738502362219</v>
       </c>
       <c r="E4" s="4">
-        <v>20.69727891156463</v>
+        <v>28.42857142857143</v>
       </c>
       <c r="F4" s="4">
-        <v>24.53355704697987</v>
+        <v>35.12248322147651</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1412296149112278</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2685501800787519</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1987996025575774</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9200869959107674</v>
+        <v>0.4265709362274067</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3256373312315635</v>
+        <v>0.2468486772273062</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4481464880643025</v>
+        <v>0.2172344818673708</v>
       </c>
       <c r="E5" s="4">
-        <v>24.70359572400391</v>
+        <v>33.15111758989314</v>
       </c>
       <c r="F5" s="4">
-        <v>25.65995525727091</v>
+        <v>37.21716203259815</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4265709362274067</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2468486772273062</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3501,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3520,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3562,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,116 +3593,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6122476303386284</v>
+        <v>0.5708876305624691</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6471018226946986</v>
+        <v>0.6252828977480893</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6533209943578248</v>
+        <v>0.6416735553548568</v>
       </c>
       <c r="E3" s="4">
-        <v>87.56462585034014</v>
+        <v>92.078231292517</v>
       </c>
       <c r="F3" s="4">
-        <v>85.38310961968678</v>
+        <v>87.3434004474273</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6252828977480893</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2117443696095063</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1966863780298575</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3887617308211432</v>
+        <v>0.4671414922135774</v>
       </c>
       <c r="C4" s="4">
-        <v>0.411373359525205</v>
+        <v>0.5076191686266802</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3660308707069916</v>
+        <v>0.4697739470315853</v>
       </c>
       <c r="E4" s="4">
-        <v>87.12074829931973</v>
+        <v>91.69387755102041</v>
       </c>
       <c r="F4" s="4">
-        <v>82.96979865771814</v>
+        <v>85.63982102908277</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.5076191686266802</v>
+      </c>
+      <c r="O4" s="5">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.167646402949936</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1589609081710415</v>
+      </c>
+      <c r="R4" s="5">
+        <v>16</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6273040257854851</v>
+        <v>0.8612211663198137</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4810924290518059</v>
+        <v>0.6779407707255439</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5023607626634801</v>
+        <v>0.7226700843902343</v>
       </c>
       <c r="E5" s="4">
-        <v>85.78474246841601</v>
+        <v>87.00680272108823</v>
       </c>
       <c r="F5" s="4">
-        <v>79.5909236177677</v>
+        <v>80.50814956855348</v>
       </c>
       <c r="G5" s="5">
         <v>14</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -3074,9 +3770,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.6779407707255439</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2782285577589744</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1362797530986263</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3801,1464 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6401106538332415</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2744333715517371</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2634276734820404</v>
+      </c>
+      <c r="E3" s="4">
+        <v>18.81122448979592</v>
+      </c>
+      <c r="F3" s="4">
+        <v>20.70693512304251</v>
+      </c>
+      <c r="G3" s="5">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>17</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6401106538332415</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2744333715517371</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.8103680462182016</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2706910995568245</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4172317315680235</v>
+      </c>
+      <c r="E4" s="4">
+        <v>20.69727891156463</v>
+      </c>
+      <c r="F4" s="4">
+        <v>24.53355704697987</v>
+      </c>
+      <c r="G4" s="5">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>16</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8103680462182016</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2706910995568245</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.9200869959107674</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3256373312315635</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4481464880643025</v>
+      </c>
+      <c r="E5" s="4">
+        <v>24.70359572400391</v>
+      </c>
+      <c r="F5" s="4">
+        <v>25.65995525727091</v>
+      </c>
+      <c r="G5" s="5">
+        <v>14</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>11</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>11</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9200869959107674</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3256373312315635</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6122476303386284</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6471018226946986</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6533209943578248</v>
+      </c>
+      <c r="E3" s="4">
+        <v>87.56462585034014</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.38310961968678</v>
+      </c>
+      <c r="G3" s="5">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5">
+        <v>17</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6471018226946986</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1826320703894533</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1738563270980977</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3887617308211432</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.411373359525205</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3660308707069916</v>
+      </c>
+      <c r="E4" s="4">
+        <v>87.12074829931973</v>
+      </c>
+      <c r="F4" s="4">
+        <v>82.96979865771814</v>
+      </c>
+      <c r="G4" s="5">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <v>17</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3988972684845331</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1644777690072055</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.163183515171276</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6273040257854851</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4810924290518059</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5023607626634801</v>
+      </c>
+      <c r="E5" s="4">
+        <v>85.78474246841601</v>
+      </c>
+      <c r="F5" s="4">
+        <v>79.5909236177677</v>
+      </c>
+      <c r="G5" s="5">
+        <v>14</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4810924290518059</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2408991659279184</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1325625968719351</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="D3" s="3">
+        <v>79.62962962962963</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>79.62962962962963</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4488755241089458</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2322601686822104</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3085965968019795</v>
+      </c>
+      <c r="K3" s="4">
+        <v>55.06991685563109</v>
+      </c>
+      <c r="L3" s="4">
+        <v>60.60029828486149</v>
+      </c>
+      <c r="M3" s="5">
+        <v>54</v>
+      </c>
+      <c r="N3" s="5">
+        <v>711455.7731151581</v>
+      </c>
+      <c r="O3" s="4">
+        <v>41.49397953546939</v>
+      </c>
+      <c r="P3" s="5">
+        <v>17146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>61.11111111111111</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="D4" s="3">
+        <v>37.03703703703704</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>37.03703703703704</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3792044829046566</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.4111635267427061</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3483003844488308</v>
+      </c>
+      <c r="K4" s="4">
+        <v>85.1618795666415</v>
+      </c>
+      <c r="L4" s="4">
+        <v>77.54101416853074</v>
+      </c>
+      <c r="M4" s="5">
+        <v>54</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1562952.919960022</v>
+      </c>
+      <c r="O4" s="4">
+        <v>134.2512386153601</v>
+      </c>
+      <c r="P4" s="5">
+        <v>11642</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="D5" s="3">
+        <v>12.96296296296296</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>12.96296296296296</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2340342362038021</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2030461143064163</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2126775523368451</v>
+      </c>
+      <c r="K5" s="4">
+        <v>85.34706475182655</v>
+      </c>
+      <c r="L5" s="4">
+        <v>82.81299196287884</v>
+      </c>
+      <c r="M5" s="5">
+        <v>54</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2036761.655330658</v>
+      </c>
+      <c r="O5" s="4">
+        <v>189.4662004958751</v>
+      </c>
+      <c r="P5" s="5">
+        <v>10750</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="C6" s="3">
+        <v>7.407407407407407</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.407407407407407</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>7.407407407407407</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2380161456400515</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2114975957522267</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2105942148769602</v>
+      </c>
+      <c r="K6" s="4">
+        <v>88.62307886117387</v>
+      </c>
+      <c r="L6" s="4">
+        <v>85.0269284944893</v>
+      </c>
+      <c r="M6" s="5">
+        <v>54</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1474976.78232193</v>
+      </c>
+      <c r="O6" s="4">
+        <v>150.6000390363417</v>
+      </c>
+      <c r="P6" s="5">
+        <v>9794</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2066096456618638</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1798683333200115</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1885273013723644</v>
+      </c>
+      <c r="K7" s="4">
+        <v>92.92139077853329</v>
+      </c>
+      <c r="L7" s="4">
+        <v>87.83598475432858</v>
+      </c>
+      <c r="M7" s="5">
+        <v>54</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4857508.912801743</v>
+      </c>
+      <c r="O7" s="4">
+        <v>663.7754731896341</v>
+      </c>
+      <c r="P7" s="5">
+        <v>7318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>72.22222222222221</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2880013230724389</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2250237357758225</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2258430476401821</v>
+      </c>
+      <c r="K8" s="4">
+        <v>88.65835222978073</v>
+      </c>
+      <c r="L8" s="4">
+        <v>80.20382798906211</v>
+      </c>
+      <c r="M8" s="5">
+        <v>54</v>
+      </c>
+      <c r="N8" s="5">
+        <v>403170.7570552826</v>
+      </c>
+      <c r="O8" s="4">
+        <v>38.28782118283785</v>
+      </c>
+      <c r="P8" s="5">
+        <v>10530</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>87.03703703703704</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>12.96296296296296</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12.96296296296296</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3501454730822933</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2643964451173273</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3138701172121936</v>
+      </c>
+      <c r="K9" s="4">
+        <v>88.7150415721845</v>
+      </c>
+      <c r="L9" s="4">
+        <v>83.47626149639417</v>
+      </c>
+      <c r="M9" s="5">
+        <v>54</v>
+      </c>
+      <c r="N9" s="5">
+        <v>550506.5805912018</v>
+      </c>
+      <c r="O9" s="4">
+        <v>56.28901642036828</v>
+      </c>
+      <c r="P9" s="5">
+        <v>9780</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C10" s="3">
+        <v>7.407407407407407</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1332134917263919</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.118886643082258</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.120158858717787</v>
+      </c>
+      <c r="K10" s="4">
+        <v>91.65847820609667</v>
+      </c>
+      <c r="L10" s="4">
+        <v>88.21671223796341</v>
+      </c>
+      <c r="M10" s="5">
+        <v>54</v>
+      </c>
+      <c r="N10" s="5">
+        <v>728765.9356594086</v>
+      </c>
+      <c r="O10" s="4">
+        <v>87.45541049554885</v>
+      </c>
+      <c r="P10" s="5">
+        <v>8333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>75.92592592592592</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="D11" s="3">
+        <v>20.37037037037037</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>20.37037037037037</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2572237016962668</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2376467701697843</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2414099229458809</v>
+      </c>
+      <c r="K11" s="4">
+        <v>85.21164021163987</v>
+      </c>
+      <c r="L11" s="4">
+        <v>79.12730963625719</v>
+      </c>
+      <c r="M11" s="5">
+        <v>54</v>
+      </c>
+      <c r="N11" s="5">
+        <v>818669.1610813141</v>
+      </c>
+      <c r="O11" s="4">
+        <v>73.98727167476855</v>
+      </c>
+      <c r="P11" s="5">
+        <v>11065</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>79.62962962962963</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>20.37037037037037</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>20.37037037037037</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2197606193649985</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1830407682574461</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1925952007438993</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.31279919375106</v>
+      </c>
+      <c r="L12" s="4">
+        <v>83.043955588698</v>
+      </c>
+      <c r="M12" s="5">
+        <v>54</v>
+      </c>
+      <c r="N12" s="5">
+        <v>395197.6673603058</v>
+      </c>
+      <c r="O12" s="4">
+        <v>40.62058457809701</v>
+      </c>
+      <c r="P12" s="5">
+        <v>9729</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>48.14814814814815</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="D13" s="3">
+        <v>48.14814814814815</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>48.14814814814815</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2802766627728748</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2623977323185707</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2536539803907025</v>
+      </c>
+      <c r="K13" s="4">
+        <v>78.31065759637194</v>
+      </c>
+      <c r="L13" s="4">
+        <v>75.89361173253749</v>
+      </c>
+      <c r="M13" s="5">
+        <v>54</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1205536.176919937</v>
+      </c>
+      <c r="O13" s="4">
+        <v>88.9891619487663</v>
+      </c>
+      <c r="P13" s="5">
+        <v>13547</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>25.92592592592592</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>74.07407407407408</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>74.07407407407408</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3490664614389093</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2289412903553357</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.2296122716081272</v>
+      </c>
+      <c r="K14" s="4">
+        <v>29.20823885109604</v>
+      </c>
+      <c r="L14" s="4">
+        <v>34.63045819869078</v>
+      </c>
+      <c r="M14" s="5">
+        <v>54</v>
+      </c>
+      <c r="N14" s="5">
+        <v>25643828.21989059</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1039.769217852272</v>
+      </c>
+      <c r="P14" s="5">
+        <v>24663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>75.92592592592592</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="D15" s="3">
+        <v>20.37037037037037</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>20.37037037037037</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2126484307373054</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1687042526122444</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1881297979254079</v>
+      </c>
+      <c r="K15" s="4">
+        <v>90.62106324011104</v>
+      </c>
+      <c r="L15" s="4">
+        <v>84.94034302759077</v>
+      </c>
+      <c r="M15" s="5">
+        <v>54</v>
+      </c>
+      <c r="N15" s="5">
+        <v>7782353.778600693</v>
+      </c>
+      <c r="O15" s="4">
+        <v>925.8093955032945</v>
+      </c>
+      <c r="P15" s="5">
+        <v>8406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>14.81481481481481</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="D16" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="F16" s="3">
+        <v>81.48148148148148</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.7757554063662888</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2853632254742374</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.3682822024796575</v>
+      </c>
+      <c r="K16" s="4">
+        <v>21.03741496598641</v>
+      </c>
+      <c r="L16" s="4">
+        <v>23.40831883337466</v>
+      </c>
+      <c r="M16" s="5">
+        <v>54</v>
+      </c>
+      <c r="N16" s="5">
+        <v>6295812.14594841</v>
+      </c>
+      <c r="O16" s="4">
+        <v>167.215004805939</v>
+      </c>
+      <c r="P16" s="5">
+        <v>37651</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>81.48148148148148</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="D17" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1910145390911858</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1603478019840614</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1669555175563082</v>
+      </c>
+      <c r="K17" s="4">
+        <v>86.93877551020397</v>
+      </c>
+      <c r="L17" s="4">
+        <v>82.98761289253365</v>
+      </c>
+      <c r="M17" s="5">
+        <v>54</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1857541.911125183</v>
+      </c>
+      <c r="O17" s="4">
+        <v>179.6983564985183</v>
+      </c>
+      <c r="P17" s="5">
+        <v>10337</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3778,16 +5944,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6013,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>43</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>43</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>23</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>20</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>45</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>7</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>48</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>39</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>15</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>47</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>48</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>41</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>11</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>11</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>26</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>26</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>5</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>40</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>40</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>40</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>41</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>11</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>11</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>2</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>45</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>44</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>44</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>44</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>9</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>9</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6781,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6823,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6854,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4826812911420689</v>
@@ -3960,10 +6913,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4826812911420689</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1887393281486235</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3954495454997385</v>
@@ -4001,10 +6970,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.002930548076449213</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.393691216653869</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2561274421687358</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4794162961403085</v>
@@ -4042,9 +7029,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4794162961403085</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2434863228503445</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7058,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7077,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7119,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7150,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4632086563911543</v>
@@ -4173,10 +7209,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1638483214754863</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4006059334257963</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3831874576022649</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4275000559699464</v>
@@ -4214,10 +7268,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3114573444888862</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3449231296230152</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4229643239923273</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.532816263455284</v>
@@ -4255,9 +7327,27 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.573849084950479</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3976043439910873</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4468857268813807</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7358,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7377,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7419,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7450,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4259211257404246</v>
@@ -4386,10 +7509,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4194253674888557</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2147972491618788</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2020602518274504</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3039999283338943</v>
@@ -4427,10 +7568,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2848028866371395</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2052568128090614</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2022499486713735</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.448679719339363</v>
@@ -4468,9 +7627,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3019474392478369</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3026262511133219</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2066101705344335</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7658,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7677,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7719,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7750,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3258495598596227</v>
@@ -4599,10 +7809,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2538574631075849</v>
+      </c>
+      <c r="O3" s="5">
+        <v>19</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.259255853618812</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2547502017858163</v>
+      </c>
+      <c r="R3" s="5">
+        <v>19</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.217124247143704</v>
@@ -4640,10 +7868,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.08775322521869573</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1968947626894078</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1876034050108046</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2673947570737027</v>
@@ -4681,9 +7927,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.01875437286453361</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2664185384570276</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1679749200530486</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7958,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7977,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8019,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8050,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.354281645671145</v>
@@ -4812,10 +8109,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3747195450138305</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2109006706653442</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1908122565914123</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1819685534391624</v>
@@ -4853,10 +8168,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1124043552591824</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.175794822518183</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.178810855384791</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2681011585219072</v>
@@ -4894,9 +8227,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1064924145601391</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2445007858621498</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1650386653157412</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8258,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3144408323398261</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2615481180108551</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2934816848664016</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.41326530612245</v>
-      </c>
-      <c r="F3" s="4">
-        <v>81.61241610738254</v>
-      </c>
-      <c r="G3" s="5">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>5</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2449440356434071</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.230994259459507</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2144153492534156</v>
-      </c>
-      <c r="E4" s="4">
-        <v>90.5204081632653</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.25503355704699</v>
-      </c>
-      <c r="G4" s="5">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5">
-        <v>15</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>5</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3204985249105499</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2152585811838937</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2456287359136822</v>
-      </c>
-      <c r="E5" s="4">
-        <v>84.91982507288635</v>
-      </c>
-      <c r="F5" s="4">
-        <v>75.26126558005875</v>
-      </c>
-      <c r="G5" s="5">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4674147311402407</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4187054574128745</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3877101962092297</v>
-      </c>
-      <c r="E3" s="4">
-        <v>88.79421768707483</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.31487695749439</v>
-      </c>
-      <c r="G3" s="5">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5">
-        <v>17</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4326521421641673</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4455660431316376</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4199537779063547</v>
-      </c>
-      <c r="E4" s="4">
-        <v>89.96258503401361</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.5592841163311</v>
-      </c>
-      <c r="G4" s="5">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5">
-        <v>19</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6172616482573565</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6432100971270607</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6276417119954983</v>
-      </c>
-      <c r="E5" s="4">
-        <v>86.81972789115653</v>
-      </c>
-      <c r="F5" s="4">
-        <v>79.30249280920302</v>
-      </c>
-      <c r="G5" s="5">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5">
-        <v>11</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/Baserarole2024.xlsx
+++ b/public/downloads/Baserarole2024.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1746248426451662</v>
+        <v>-0.1339903863548324</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2998088782463817</v>
+        <v>0.2945292338887739</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2402235196532846</v>
+        <v>0.2358929575958298</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.03155434850083812</v>
+        <v>0.04803429355992606</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2417886007933233</v>
+        <v>0.2411791054518602</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2246833897593394</v>
+        <v>0.2227720663001162</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1227158976524091</v>
+        <v>0.07975905819460571</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3371515617941143</v>
+        <v>0.32367122686767</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2002580060075241</v>
+        <v>0.1936075426078785</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3561315991860751</v>
+        <v>0.4610536669640624</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3744568127597489</v>
+        <v>0.3801981374784958</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2550404511267192</v>
+        <v>0.2432792917761885</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3488323414972629</v>
+        <v>0.3576383859051475</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
@@ -1925,7 +1925,7 @@
         <v>0.3084969334062066</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2965167527812968</v>
+        <v>0.2960532767598292</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6432100971270607</v>
+        <v>0.6451531463067113</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3749129016517666</v>
+        <v>0.3749291765066687</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.223375177137774</v>
+        <v>0.2228659680859266</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2306733230146552</v>
+        <v>-0.240951001895823</v>
       </c>
       <c r="O3" s="5">
         <v>19</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1368690918498356</v>
+        <v>0.1358413239617188</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1403480377341195</v>
+        <v>0.1398071072666897</v>
       </c>
       <c r="R3" s="5">
         <v>19</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1728167069219769</v>
+        <v>-0.1775962034369307</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1204728463818312</v>
+        <v>0.119853049534443</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1187793058347875</v>
+        <v>0.1183784405488501</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.18833311991302</v>
+        <v>-0.156530386707928</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1461921277565588</v>
+        <v>0.1471451959522313</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07831393401391509</v>
+        <v>0.07328768284683811</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3114666796215726</v>
+        <v>-0.2913702014624278</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
@@ -2516,13 +2516,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1226933186962746</v>
+        <v>-0.112007224062495</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2216865622001755</v>
+        <v>0.2195493432734196</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2398429100390409</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.0009586056947088966</v>
+        <v>-0.07182464829833179</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3098209202188525</v>
+        <v>0.3085751631417273</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2800188722839453</v>
+        <v>0.2719318440624963</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4797088952417017</v>
+        <v>-0.4768271708276757</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2311474120835174</v>
+        <v>-0.2356342476075497</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
@@ -2825,7 +2825,7 @@
         <v>0.1788300385312226</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1622481054352048</v>
+        <v>0.1619841739337911</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3390617226577263</v>
+        <v>-0.3886982029663386</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2567793438984268</v>
+        <v>0.2343488879129398</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1907026441343794</v>
+        <v>0.1692273018164201</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3164499841596495</v>
+        <v>-0.247156277390161</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3030659822812097</v>
+        <v>0.2699269163652162</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2395204641468217</v>
+        <v>0.2286772977304253</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -3116,13 +3116,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3115584207436143</v>
+        <v>-0.3327056489428202</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2602623890109032</v>
+        <v>0.266606557470665</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2772274655976218</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4376405310660895</v>
+        <v>-0.4985168229736132</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2763123117066416</v>
+        <v>0.3020517128375835</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2758102904730669</v>
+        <v>0.2749926012044075</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1412296149112278</v>
+        <v>0.1753359922205038</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2685501800787519</v>
+        <v>0.2518056639178398</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1987996025575774</v>
+        <v>0.1911409115037776</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -3653,16 +3653,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6252828977480893</v>
+        <v>-0.5773647194156108</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2117443696095063</v>
+        <v>0.2011136913592246</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1966863780298575</v>
+        <v>0.1909913515808201</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -3712,13 +3712,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5076191686266802</v>
+        <v>-0.5033127641811248</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.167646402949936</v>
+        <v>0.1667851220608249</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1589609081710415</v>
@@ -3771,16 +3771,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6779407707255439</v>
+        <v>-0.7056253011579017</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2782285577589744</v>
+        <v>0.2699713345516308</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1362797530986263</v>
+        <v>0.1316726520921697</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4247,16 +4247,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6471018226946986</v>
+        <v>-0.5851437146122684</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1826320703894533</v>
+        <v>0.1674483583489094</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1738563270980977</v>
+        <v>0.1669269202414161</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -4306,16 +4306,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3988972684845331</v>
+        <v>-0.3897228856628558</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1644777690072055</v>
+        <v>0.1635603307250378</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.163183515171276</v>
+        <v>0.1626438455935303</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -4365,16 +4365,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4810924290518059</v>
+        <v>-0.4973550779839613</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2408991659279184</v>
+        <v>0.2359013087912117</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1325625968719351</v>
+        <v>0.1320706564534078</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -4511,13 +4511,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4488755241089458</v>
+        <v>0.4624276344005935</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2322601686822104</v>
+        <v>0.2254841135363866</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3085965968019795</v>
+        <v>0.3176313369964113</v>
       </c>
       <c r="K3" s="4">
         <v>55.06991685563109</v>
@@ -4561,13 +4561,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3792044829046566</v>
+        <v>0.3704863982161894</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4111635267427061</v>
+        <v>0.3918382883479048</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3483003844488308</v>
+        <v>0.3737246403405371</v>
       </c>
       <c r="K4" s="4">
         <v>85.1618795666415</v>
@@ -4611,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2340342362038021</v>
+        <v>0.2337200610460265</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2030461143064163</v>
+        <v>0.2026711961650581</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2126775523368451</v>
+        <v>0.2116755876964612</v>
       </c>
       <c r="K5" s="4">
         <v>85.34706475182655</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2380161456400515</v>
+        <v>0.2367908003414085</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2114975957522267</v>
+        <v>0.2083026640115246</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2105942148769602</v>
+        <v>0.213839663993922</v>
       </c>
       <c r="K6" s="4">
         <v>88.62307886117387</v>
@@ -4711,13 +4711,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2066096456618638</v>
+        <v>0.2011781954036207</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1798683333200115</v>
+        <v>0.1766443293798551</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1885273013723644</v>
+        <v>0.189977935454268</v>
       </c>
       <c r="K7" s="4">
         <v>92.92139077853329</v>
@@ -4761,13 +4761,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2880013230724389</v>
+        <v>0.2823252585733345</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2250237357758225</v>
+        <v>0.2210882882541051</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2258430476401821</v>
+        <v>0.2297349260686649</v>
       </c>
       <c r="K8" s="4">
         <v>88.65835222978073</v>
@@ -4811,13 +4811,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3501454730822933</v>
+        <v>0.3522761090516187</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2643964451173273</v>
+        <v>0.2598358695229181</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3138701172121936</v>
+        <v>0.3244521103597741</v>
       </c>
       <c r="K9" s="4">
         <v>88.7150415721845</v>
@@ -4861,13 +4861,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1332134917263919</v>
+        <v>0.1328503743195273</v>
       </c>
       <c r="I10" s="4">
-        <v>0.118886643082258</v>
+        <v>0.1174667132700757</v>
       </c>
       <c r="J10" s="4">
-        <v>0.120158858717787</v>
+        <v>0.1174446260099629</v>
       </c>
       <c r="K10" s="4">
         <v>91.65847820609667</v>
@@ -4911,13 +4911,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2572237016962668</v>
+        <v>0.2561091650737692</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2376467701697843</v>
+        <v>0.2358715688528809</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2414099229458809</v>
+        <v>0.2414578903481278</v>
       </c>
       <c r="K11" s="4">
         <v>85.21164021163987</v>
@@ -4961,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2197606193649985</v>
+        <v>0.2139453159613538</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1830407682574461</v>
+        <v>0.17794215758992</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1925952007438993</v>
+        <v>0.1892003928474727</v>
       </c>
       <c r="K12" s="4">
         <v>89.31279919375106</v>
@@ -5011,13 +5011,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2802766627728748</v>
+        <v>0.2770258047489591</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2623977323185707</v>
+        <v>0.258038586173343</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2536539803907025</v>
+        <v>0.2653208529314878</v>
       </c>
       <c r="K13" s="4">
         <v>78.31065759637194</v>
@@ -5061,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3490664614389093</v>
+        <v>0.3428647887867197</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2289412903553357</v>
+        <v>0.2256589941894215</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2296122716081272</v>
+        <v>0.2292760410874879</v>
       </c>
       <c r="K14" s="4">
         <v>29.20823885109604</v>
@@ -5111,13 +5111,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2126484307373054</v>
+        <v>0.206251388002293</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1687042526122444</v>
+        <v>0.1654704884112028</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1881297979254079</v>
+        <v>0.1896666240430017</v>
       </c>
       <c r="K15" s="4">
         <v>90.62106324011104</v>
@@ -5211,13 +5211,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1910145390911858</v>
+        <v>0.1837554093436279</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1603478019840614</v>
+        <v>0.1573502178120038</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1669555175563082</v>
+        <v>0.1723612349157249</v>
       </c>
       <c r="K17" s="4">
         <v>86.93877551020397</v>
@@ -6971,16 +6971,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.002930548076449213</v>
+        <v>-0.05805394823596544</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.393691216653869</v>
+        <v>0.4302819144413178</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2561274421687358</v>
+        <v>0.2439305429062529</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7210,16 +7210,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1638483214754863</v>
+        <v>0.3535393198791326</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4006059334257963</v>
+        <v>0.3798735810135866</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3831874576022649</v>
+        <v>0.3396397358478416</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -7269,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3114573444888862</v>
+        <v>0.3751535295488964</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
@@ -7328,16 +7328,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>1.573849084950479</v>
+        <v>1.601913847416995</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3976043439910873</v>
+        <v>0.3935950922101564</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4468857268813807</v>
+        <v>0.44287647510045</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7510,16 +7510,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4194253674888557</v>
+        <v>-0.3872722748484705</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2147972491618788</v>
+        <v>0.2147438122611675</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2020602518274504</v>
+        <v>0.2020008774933267</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -7569,13 +7569,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2848028866371395</v>
+        <v>-0.2768545263843123</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2052568128090614</v>
+        <v>0.2044619767837787</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2022499486713735</v>
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3019474392478369</v>
+        <v>-0.2861448609009472</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
@@ -7637,7 +7637,7 @@
         <v>0.3026262511133219</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2066101705344335</v>
+        <v>0.2048543284958902</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -7810,16 +7810,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2538574631075849</v>
+        <v>-0.219965226693148</v>
       </c>
       <c r="O3" s="5">
         <v>19</v>
       </c>
       <c r="P3" s="4">
-        <v>0.259255853618812</v>
+        <v>0.2525217677187356</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2547502017858163</v>
+        <v>0.249445492228601</v>
       </c>
       <c r="R3" s="5">
         <v>19</v>
@@ -7869,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08775322521869573</v>
+        <v>-0.08953988479549935</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
@@ -7928,16 +7928,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.01875437286453361</v>
+        <v>0.02742300562067612</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2664185384570276</v>
+        <v>0.2713123293052279</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1679749200530486</v>
+        <v>0.1628441002213587</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -8110,16 +8110,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3747195450138305</v>
+        <v>-0.3054464826050207</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2109006706653442</v>
+        <v>0.1970868761835845</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1908122565914123</v>
+        <v>0.1831606029904359</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -8169,16 +8169,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1124043552591824</v>
+        <v>-0.08046371447143486</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.175794822518183</v>
+        <v>0.1749437013026864</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.178810855384791</v>
+        <v>0.1778651651453503</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1064924145601391</v>
+        <v>-0.1109776350060656</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
